--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486349_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486349_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.987</v>
+        <v>8.2386</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6418</v>
+        <v>3.2632</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3453</v>
+        <v>4.9754</v>
       </c>
       <c r="G2" t="n">
         <v>4.2568</v>
@@ -610,13 +610,13 @@
         <v>4.1326</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7074</v>
+        <v>0.9589</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6117</v>
+        <v>0.2331</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0957</v>
+        <v>0.7258</v>
       </c>
       <c r="V2" t="n">
         <v>0.1952</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5043</v>
+        <v>3.2954</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.617</v>
+        <v>-0.5485</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1213</v>
+        <v>3.8439</v>
       </c>
       <c r="G3" t="n">
         <v>2.0076</v>
@@ -688,13 +688,13 @@
         <v>3.0451</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1285</v>
+        <v>0.9196</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1406</v>
+        <v>0.2091</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9879</v>
+        <v>0.7105</v>
       </c>
       <c r="V3" t="n">
         <v>0.5857</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8391</v>
+        <v>1.2553</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.741</v>
+        <v>-0.294</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5802</v>
+        <v>1.5493</v>
       </c>
       <c r="G4" t="n">
         <v>-0.548</v>
@@ -766,13 +766,13 @@
         <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3306</v>
+        <v>0.0856</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3544</v>
+        <v>0.3235</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>D. SANADZE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2817</v>
+        <v>0.9053</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2264</v>
+        <v>0.4673</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5081</v>
+        <v>0.438</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9506</v>
+        <v>-0.3059</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8334</v>
+        <v>0.5595</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1171</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8622</v>
+        <v>0.8537</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1737</v>
+        <v>0.2983</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6885</v>
+        <v>0.5554</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0883</v>
+        <v>-1.1596</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6597</v>
+        <v>0.2612</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5714</v>
+        <v>-1.4208</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>-5.4377</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0706</v>
+        <v>-0.1761</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8482</v>
+        <v>-0.0336</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2224</v>
+        <v>-0.1424</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8695</v>
+        <v>5.0849</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.5443</v>
+        <v>5.0849</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1696</v>
+        <v>0.4848</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.0811</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1696</v>
+        <v>1.5659</v>
       </c>
       <c r="G6" t="n">
-        <v>0.149</v>
+        <v>1.6639</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.8129</v>
       </c>
       <c r="I6" t="n">
-        <v>0.149</v>
+        <v>-0.149</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.7134</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.8248</v>
       </c>
       <c r="M6" t="n">
-        <v>0.149</v>
+        <v>-0.0496</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.9242</v>
       </c>
       <c r="O6" t="n">
-        <v>0.149</v>
+        <v>-0.9738</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.5676</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.6976</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0205</v>
+        <v>0.256</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.0781</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0205</v>
+        <v>0.1778</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SANADZE</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0931</v>
+        <v>0.2004</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2531</v>
+        <v>0.2004</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3059</v>
+        <v>0.149</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5595</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8653999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8537</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2983</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5554</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1596</v>
+        <v>0.149</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2612</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4208</v>
+        <v>0.149</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.6976</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.4377</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9883</v>
+        <v>0.0514</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6609</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3274</v>
+        <v>0.0514</v>
       </c>
       <c r="V7" t="n">
-        <v>5.0849</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>5.0849</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CHAPELA LAGE</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0801</v>
+        <v>0.1968</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8302</v>
+        <v>-0.3728</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7501</v>
+        <v>0.5695</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5166</v>
+        <v>-1.3636</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9947</v>
+        <v>-2.0681</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5219</v>
+        <v>0.7044</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4192</v>
+        <v>0.0366</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0182</v>
+        <v>-0.9212</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4374</v>
+        <v>0.9578</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0974</v>
+        <v>-1.4003</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0129</v>
+        <v>-1.1468</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.2534</v>
       </c>
       <c r="P8" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="S8" t="n">
-        <v>0.262</v>
+        <v>0.8851</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.411</v>
+        <v>0.1779</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7395</v>
+        <v>-1.4997</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>A. CHAPELA LAGE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2791</v>
+        <v>-0.053</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.4949</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6105</v>
+        <v>0.4419</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5685</v>
+        <v>-1.5166</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4513</v>
+        <v>-0.9947</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1172</v>
+        <v>-0.5219</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.4822</v>
+        <v>-0.4192</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8519</v>
+        <v>0.0182</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6303</v>
+        <v>-0.4374</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0863</v>
+        <v>-1.0974</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5994</v>
+        <v>-1.0129</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4869</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6374</v>
+        <v>0.289</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7677</v>
+        <v>-0.0757</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1303</v>
+        <v>0.3647</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8695</v>
+        <v>0.7395</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0.7395</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6472</v>
+        <v>-0.7366</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1551</v>
+        <v>-1.2755</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5079</v>
+        <v>0.5389</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3636</v>
+        <v>0.9506</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0681</v>
+        <v>0.8334</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7044</v>
+        <v>0.1171</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0366</v>
+        <v>0.8622</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9212</v>
+        <v>0.1737</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9578</v>
+        <v>0.6885</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4003</v>
+        <v>0.0883</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1468</v>
+        <v>0.6597</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2534</v>
+        <v>-0.5714</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1751</v>
+        <v>-0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0411</v>
+        <v>1.0524</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6044</v>
+        <v>0.7991</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6455</v>
+        <v>0.2532</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4997</v>
+        <v>-1.8695</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3698</v>
+        <v>-0.5443</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7474</v>
+        <v>-1.3235</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8202</v>
+        <v>-2.1189</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0728</v>
+        <v>0.7955</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6639</v>
+        <v>-3.5685</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8129</v>
+        <v>-2.4513</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.149</v>
+        <v>-1.1172</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7134</v>
+        <v>-2.4822</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8885999999999999</v>
+        <v>-1.8519</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8248</v>
+        <v>-0.6303</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0496</v>
+        <v>-1.0863</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9242</v>
+        <v>-0.5994</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9738</v>
+        <v>-0.4869</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5676</v>
+        <v>-1.305</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6976</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9762999999999999</v>
+        <v>0.593</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6609</v>
+        <v>0.5384</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3153</v>
+        <v>0.0547</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.8695</v>
       </c>
       <c r="W11" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2599</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="12">
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.121</v>
+        <v>12.4635</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7977</v>
+        <v>-2.4552</v>
       </c>
       <c r="F12" t="n">
-        <v>14.9189</v>
+        <v>14.9187</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7253</v>
+        <v>1.725299999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5698</v>
+        <v>2.569800000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8448000000000001</v>
+        <v>-0.8447999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>7.459899999999999</v>
@@ -1375,10 +1375,10 @@
         <v>-5.7349</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4433999999999997</v>
+        <v>-0.4434</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.291399999999999</v>
+        <v>-5.2914</v>
       </c>
       <c r="P12" t="n">
         <v>1.0876</v>
@@ -1390,16 +1390,16 @@
         <v>20.6631</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5723</v>
+        <v>4.914899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.346</v>
+        <v>1.6885</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2263</v>
+        <v>3.2264</v>
       </c>
       <c r="V12" t="n">
-        <v>4.735800000000001</v>
+        <v>4.7358</v>
       </c>
       <c r="W12" t="n">
         <v>7.971900000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1379</v>
+        <v>3.2298</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0209</v>
+        <v>0.6914</v>
       </c>
       <c r="F13" t="n">
-        <v>2.117</v>
+        <v>2.5384</v>
       </c>
       <c r="G13" t="n">
         <v>3.472</v>
@@ -1468,13 +1468,13 @@
         <v>3.4801</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7023</v>
+        <v>-0.6105</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3459</v>
+        <v>-0.6753</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3564</v>
+        <v>0.0649</v>
       </c>
       <c r="V13" t="n">
         <v>0.5857</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0993</v>
+        <v>1.3866</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7358</v>
+        <v>-0.5848</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3634</v>
+        <v>1.9713</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5997</v>
+        <v>-1.2381</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3774</v>
+        <v>0.4289</v>
       </c>
       <c r="I14" t="n">
-        <v>1.977</v>
+        <v>-1.667</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1028</v>
+        <v>-1.1153</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7879</v>
+        <v>0.2983</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3149</v>
+        <v>-1.4136</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5031</v>
+        <v>-0.1228</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1652</v>
+        <v>0.1306</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3379</v>
+        <v>-0.2534</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.6101</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0224</v>
+        <v>-0.2448</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8868</v>
+        <v>-0.0769</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1356</v>
+        <v>-0.1679</v>
       </c>
       <c r="V14" t="n">
+        <v>2.4345</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="X14" t="n">
         <v>0.7395</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.3904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5748</v>
+        <v>1.2625</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0318</v>
+        <v>0.8476</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6066</v>
+        <v>0.4149</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2381</v>
+        <v>1.5997</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4289</v>
+        <v>-0.3774</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.667</v>
+        <v>1.977</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1153</v>
+        <v>3.1028</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2983</v>
+        <v>0.7879</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4136</v>
+        <v>2.3149</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1228</v>
+        <v>-1.5031</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1306</v>
+        <v>-1.1652</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2534</v>
+        <v>-0.3379</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>-2.6101</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0566</v>
+        <v>-0.8592</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5239</v>
+        <v>-0.7751</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5327</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4345</v>
+        <v>0.7395</v>
       </c>
       <c r="W15" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7395</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2366</v>
+        <v>0.1044</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1338</v>
+        <v>0.6374</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8972</v>
+        <v>-0.533</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6443</v>
+        <v>2.0176</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3223</v>
+        <v>-0.8853</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9666</v>
+        <v>2.903</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1749</v>
+        <v>2.9398</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0912</v>
+        <v>-0.5991</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2661</v>
+        <v>3.5389</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4694</v>
+        <v>-0.9222</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2311</v>
+        <v>-0.2863</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7004</v>
+        <v>-0.6359</v>
       </c>
       <c r="P16" t="n">
         <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1408</v>
+        <v>-0.6979</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3087</v>
+        <v>-0.7799</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1679</v>
+        <v>0.082</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.13</v>
+        <v>-2.0854</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0607</v>
+        <v>-0.3415</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8609</v>
+        <v>0.4632</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8002</v>
+        <v>-0.8047</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0176</v>
+        <v>-0.6443</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8853</v>
+        <v>0.3223</v>
       </c>
       <c r="I17" t="n">
-        <v>2.903</v>
+        <v>-0.9666</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9398</v>
+        <v>-0.1749</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5991</v>
+        <v>0.0912</v>
       </c>
       <c r="L17" t="n">
-        <v>3.5389</v>
+        <v>-0.2661</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9222</v>
+        <v>-0.4694</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2863</v>
+        <v>0.2311</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6359</v>
+        <v>-0.7004</v>
       </c>
       <c r="P17" t="n">
         <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7416</v>
+        <v>0.5627</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5564</v>
+        <v>0.6381</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1852</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.0854</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.0854</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2349</v>
+        <v>-0.9998</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9015</v>
+        <v>-0.7897</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3334</v>
+        <v>-0.2101</v>
       </c>
       <c r="G18" t="n">
         <v>2.5123</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3769</v>
+        <v>-0.1418</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1029</v>
+        <v>0.0204</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7602</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4714</v>
+        <v>-2.2631</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0239</v>
+        <v>-2.0226</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5526</v>
+        <v>-0.2405</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6213</v>
+        <v>-0.1021</v>
       </c>
       <c r="H19" t="n">
-        <v>0.292</v>
+        <v>0.2158</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.9133</v>
+        <v>-0.318</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9646</v>
+        <v>0.3832</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0793</v>
+        <v>0.3832</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0439</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6567</v>
+        <v>-0.4854</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2127</v>
+        <v>-0.1674</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8694</v>
+        <v>-0.318</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9576</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2571</v>
+        <v>-0.4209</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8977000000000001</v>
+        <v>-0.2307</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3594</v>
+        <v>-0.1902</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.0647</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.529</v>
+        <v>-2.2703</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1343</v>
+        <v>-2.6945</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3946</v>
+        <v>0.4242</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1021</v>
+        <v>-2.6213</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2158</v>
+        <v>0.292</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.318</v>
+        <v>-2.9133</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3832</v>
+        <v>-1.9646</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3832</v>
+        <v>0.0793</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.0439</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4854</v>
+        <v>-0.6567</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1674</v>
+        <v>0.2127</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.318</v>
+        <v>-0.8694</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6868</v>
+        <v>0.4581</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3425</v>
+        <v>0.2271</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3443</v>
+        <v>0.231</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.0647</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.376</v>
+        <v>-3.4197</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3106</v>
+        <v>-3.5341</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0654</v>
+        <v>0.1144</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2755</v>
@@ -2092,13 +2092,13 @@
         <v>2.6101</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0804</v>
+        <v>-0.1241</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0036</v>
+        <v>-0.2199</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.0958</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.619</v>
+        <v>-7.2079</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.268000000000001</v>
+        <v>-7.821</v>
       </c>
       <c r="F22" t="n">
-        <v>0.649</v>
+        <v>0.6131</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4456</v>
@@ -2170,13 +2170,13 @@
         <v>3.0451</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3034</v>
+        <v>-0.8923</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5069</v>
+        <v>-1.0599</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2036</v>
+        <v>0.1676</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.121</v>
+        <v>-10.519</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.9187</v>
+        <v>-14.8071</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7978</v>
+        <v>4.288</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.725300000000001</v>
+        <v>-1.725299999999999</v>
       </c>
       <c r="H23" t="n">
         <v>-2.57</v>
@@ -2221,7 +2221,7 @@
         <v>0.8447000000000002</v>
       </c>
       <c r="J23" t="n">
-        <v>5.734599999999999</v>
+        <v>5.734600000000001</v>
       </c>
       <c r="K23" t="n">
         <v>0.4432</v>
@@ -2248,13 +2248,13 @@
         <v>19.5756</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.5725</v>
+        <v>-2.9707</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.2264</v>
+        <v>-3.1147</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.346</v>
+        <v>0.1441</v>
       </c>
       <c r="V23" t="n">
         <v>-4.7358</v>
